--- a/data/trans_orig/P3A$yo-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Clase-trans_orig.xlsx
@@ -504,7 +504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W74"/>
+  <dimension ref="A1:W53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares según quién se ocupa principalmente de las tareas domésticas (multirrespuesta) en 2023</t>
+          <t>Hogares según quién se ocupa principalmente de las tareas domésticas (multirrespuesta) en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338965</t>
+          <t>338950</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>381336</t>
+          <t>380685</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,48%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>395936</t>
+          <t>396025</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>420512</t>
+          <t>421260</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>744026</t>
+          <t>748144</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>792634</t>
+          <t>795793</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,16%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,59%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>275528</t>
+          <t>273403</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>322919</t>
+          <t>321288</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138591</t>
+          <t>138859</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172693</t>
+          <t>172851</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>31,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426236</t>
+          <t>426355</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>483769</t>
+          <t>484205</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,82%</t>
+          <t>50,86%</t>
         </is>
       </c>
     </row>
@@ -941,112 +941,112 @@
       <c r="A6" s="1" t="n"/>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>91</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97633</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80472</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>120302</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>23,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>100822</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87018</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>117620</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>233</t>
         </is>
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>198455</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>173927</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>225831</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>23,72%</t>
         </is>
       </c>
     </row>
@@ -1054,112 +1054,112 @@
       <c r="A7" s="1" t="n"/>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4124</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>13337</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4082</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1845</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1251</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>11653</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7384</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,87%</t>
         </is>
       </c>
     </row>
@@ -1167,112 +1167,112 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>29293</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>20588</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>40618</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,8%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>4,08%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>8,04%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>31060</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>23396</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>40447</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>6,95%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>5,24%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>9,05%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>97633</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>78812</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>122121</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>19,33%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>15,6%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>24,17%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>100822</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>86215</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>120180</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>22,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>19,3%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>26,9%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>198455</t>
+          <t>60353</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>176446</t>
+          <t>48220</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>227596</t>
+          <t>74275</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>23,91%</t>
+          <t>7,8%</t>
         </is>
       </c>
     </row>
@@ -1280,112 +1280,112 @@
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7157</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>3216</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>12285</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,42%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>1191</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1748</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>3995</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,27%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>0,35%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1251</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4504</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>1,48%</t>
         </is>
       </c>
     </row>
@@ -1393,225 +1393,229 @@
       <c r="A10" s="1" t="n"/>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>5077</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4215</t>
+          <t>1622</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13224</t>
+          <t>11958</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>6817</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1692</t>
+          <t>3314</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8344</t>
+          <t>14295</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>11895</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>20626</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n"/>
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>334</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>313528</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>20912</t>
+          <t>291292</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>39378</t>
+          <t>333847</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>73,9%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>561</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>359996</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>23171</t>
+          <t>348532</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>41301</t>
+          <t>367853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>895</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>673524</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>47943</t>
+          <t>647732</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>73821</t>
+          <t>696309</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>77,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>83,46%</t>
         </is>
       </c>
     </row>
@@ -1619,112 +1623,112 @@
       <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>265</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>236580</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3677</t>
+          <t>215924</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>257682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>47,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>57,04%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>169</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>113162</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99474</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4057</t>
+          <t>129229</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>33,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>434</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>349742</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4438</t>
+          <t>322873</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>14706</t>
+          <t>377666</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>45,27%</t>
         </is>
       </c>
     </row>
@@ -1732,229 +1736,225 @@
       <c r="A13" s="1" t="n"/>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>101</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>114817</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1909</t>
+          <t>95259</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11304</t>
+          <t>137476</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>25,42%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>115</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>82999</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>68340</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>14420</t>
+          <t>98233</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>21,69%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>216</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>197816</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>175409</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>19802</t>
+          <t>227521</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>21,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>27,27%</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>Grupo III</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>334</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>313528</t>
+          <t>8699</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>291153</t>
+          <t>4775</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>335408</t>
+          <t>15505</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,45%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>561</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>359996</t>
+          <t>5755</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>348495</t>
+          <t>3135</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>368329</t>
+          <t>10612</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>2,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>895</t>
+          <t>24</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>673524</t>
+          <t>14453</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>651285</t>
+          <t>9238</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>697309</t>
+          <t>21559</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>2,58%</t>
         </is>
       </c>
     </row>
@@ -1962,112 +1962,112 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>265</t>
+          <t>20</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>236580</t>
+          <t>14767</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>214075</t>
+          <t>9219</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>260328</t>
+          <t>23390</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>169</t>
+          <t>25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>113162</t>
+          <t>12447</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>99106</t>
+          <t>8182</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>129067</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>434</t>
+          <t>45</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>349742</t>
+          <t>27214</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>320022</t>
+          <t>19118</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>377918</t>
+          <t>36334</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>45,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
     </row>
@@ -2075,112 +2075,112 @@
       <c r="A16" s="1" t="n"/>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3283</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>995</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>8215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5058</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2344</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>9851</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8342</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>15130</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -2188,225 +2188,229 @@
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>9153</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4268</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>17219</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1782</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>409</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>5012</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>12</t>
         </is>
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10936</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5682</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>18789</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>2,25%</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n"/>
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>101</t>
+          <t>316</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114817</t>
+          <t>281530</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>94981</t>
+          <t>109684</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>137588</t>
+          <t>453787</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>42,13%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>30,46%</t>
+          <t>67,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>115</t>
+          <t>267</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>151682</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>69180</t>
+          <t>141368</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>98937</t>
+          <t>157380</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>84,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
         <is>
-          <t>216</t>
+          <t>583</t>
         </is>
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>197816</t>
+          <t>433212</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>174075</t>
+          <t>202352</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>228895</t>
+          <t>620429</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>51,91%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>74,34%</t>
         </is>
       </c>
     </row>
@@ -2414,112 +2418,112 @@
       <c r="A19" s="1" t="n"/>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>278</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>241950</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>97754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>394221</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>36,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>14,63%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>43079</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>34708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>1243</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>25,9%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>31,85%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>350</t>
         </is>
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>285029</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>129610</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1496</t>
+          <t>408863</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>48,99%</t>
         </is>
       </c>
     </row>
@@ -2527,112 +2531,112 @@
       <c r="A20" s="1" t="n"/>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>88029</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4524</t>
+          <t>35637</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>15868</t>
+          <t>147620</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>35717</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2849</t>
+          <t>27068</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9991</t>
+          <t>46115</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>16,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>153</t>
         </is>
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>123745</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>8571</t>
+          <t>58610</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>21391</t>
+          <t>181840</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>14,83%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>21,79%</t>
         </is>
       </c>
     </row>
@@ -2640,112 +2644,112 @@
       <c r="A21" s="1" t="n"/>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>13877</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>9200</t>
+          <t>4197</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>21796</t>
+          <t>26438</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,82%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>8095</t>
+          <t>3768</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>18601</t>
+          <t>11013</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>32</t>
         </is>
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>20406</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>18923</t>
+          <t>8012</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>36223</t>
+          <t>32286</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -2753,112 +2757,112 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>6349</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>1684</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>8316</t>
+          <t>12994</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>13</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>6251</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2061</t>
+          <t>3335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9349</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>25</t>
         </is>
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>12600</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4490</t>
+          <t>4368</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>14062</t>
+          <t>21322</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -2866,342 +2870,342 @@
       <c r="A23" s="1" t="n"/>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>15</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9584</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4049</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>16624</t>
+          <t>19637</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>6643</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3586</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>4899</t>
+          <t>11390</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>27</t>
         </is>
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>16227</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5743</t>
+          <t>5956</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>18765</t>
+          <t>26209</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>3,14%</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A24" s="1" t="n"/>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>281530</t>
+          <t>244680</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>99734</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>453657</t>
+          <t>498119</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>14,92%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>141628</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>157492</t>
+          <t>—</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>94,68%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
-          <t>583</t>
+          <t>1</t>
         </is>
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>433212</t>
+          <t>244680</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>182404</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>619699</t>
+          <t>558002</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>21,86%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>74,25%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n"/>
+      <c r="A25" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>278</t>
+          <t>737</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>241950</t>
+          <t>698511</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>88350</t>
+          <t>664665</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>391529</t>
+          <t>731240</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>67,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>58,59%</t>
+          <t>70,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>43079</t>
+          <t>937664</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>35469</t>
+          <t>920824</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>53308</t>
+          <t>957085</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>21,32%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
         <is>
-          <t>350</t>
+          <t>1905</t>
         </is>
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>285029</t>
+          <t>1636174</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>119561</t>
+          <t>1579451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>413161</t>
+          <t>1757817</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>81,28%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>14,33%</t>
+          <t>78,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>49,5%</t>
+          <t>87,33%</t>
         </is>
       </c>
     </row>
@@ -3209,112 +3213,112 @@
       <c r="A26" s="1" t="n"/>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>599</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>528324</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>490777</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>563866</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>51,05%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>54,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>322</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>210081</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115126</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>275424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>921</t>
         </is>
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>738405</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>506191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>833683</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>25,15%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>41,42%</t>
         </is>
       </c>
     </row>
@@ -3322,112 +3326,112 @@
       <c r="A27" s="1" t="n"/>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>219</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>238937</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>207804</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>276076</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>26,68%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>313</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>208196</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>123209</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>274137</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>12,6%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>532</t>
         </is>
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>447133</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>311024</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>518608</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>25,76%</t>
         </is>
       </c>
     </row>
@@ -3435,112 +3439,112 @@
       <c r="A28" s="1" t="n"/>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>88029</t>
+          <t>45069</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>31688</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>145030</t>
+          <t>56955</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>33</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>15773</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>8503</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>46968</t>
+          <t>23983</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,24%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>102</t>
         </is>
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>123745</t>
+          <t>60841</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>51053</t>
+          <t>43506</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>183555</t>
+          <t>75403</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>3,75%</t>
         </is>
       </c>
     </row>
@@ -3548,112 +3552,112 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>23744</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>35293</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14947</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>7597</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>22472</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>60</t>
         </is>
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>25432</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2063</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -3661,112 +3665,112 @@
       <c r="A30" s="1" t="n"/>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>35</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>26977</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>18327</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>26321</t>
+          <t>40347</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>12340</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>5703</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>18832</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>63</t>
         </is>
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>39317</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>8000</t>
+          <t>26219</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>32731</t>
+          <t>53978</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -3774,225 +3778,229 @@
       <c r="A31" s="1" t="n"/>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>12773</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1603</t>
+          <t>6504</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>13338</t>
+          <t>22474</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>5588</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3415</t>
+          <t>1748</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>10648</t>
+          <t>12108</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>20</t>
         </is>
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>4812</t>
+          <t>10429</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>30110</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>1,5%</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n"/>
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>340</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>294938</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>2934</t>
+          <t>269891</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>18071</t>
+          <t>315728</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>62,09%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>56,81%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>1199</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>796658</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>3524</t>
+          <t>783655</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>11520</t>
+          <t>807936</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>94,69%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>96,03%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>1539</t>
         </is>
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>1091596</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>1061203</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>25957</t>
+          <t>1138782</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>82,92%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>80,62%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>3,11%</t>
+          <t>86,51%</t>
         </is>
       </c>
     </row>
@@ -4000,229 +4008,225 @@
       <c r="A33" s="1" t="n"/>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>247</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>213741</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>190366</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>517142</t>
+          <t>236558</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>44,99%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>49,8%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>255</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>152338</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>115670</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>180429</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>502</t>
         </is>
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>366078</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>292821</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>584324</t>
+          <t>405993</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>30,84%</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VI</t>
-        </is>
-      </c>
+      <c r="A34" s="1" t="n"/>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>737</t>
+          <t>139</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>139360</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>664453</t>
+          <t>117800</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>726619</t>
+          <t>163903</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>70,22%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>234</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>937664</t>
+          <t>143939</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>920687</t>
+          <t>108190</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>958394</t>
+          <t>168805</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>17,11%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
         <is>
-          <t>1905</t>
+          <t>373</t>
         </is>
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1636174</t>
+          <t>283299</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1578783</t>
+          <t>229222</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1748980</t>
+          <t>317858</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>78,43%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>24,15%</t>
         </is>
       </c>
     </row>
@@ -4230,112 +4234,112 @@
       <c r="A35" s="1" t="n"/>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>599</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>528324</t>
+          <t>19904</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>493957</t>
+          <t>13220</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>564752</t>
+          <t>28933</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>107</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>210081</t>
+          <t>48207</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>108909</t>
+          <t>33957</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>273785</t>
+          <t>59573</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
         <is>
-          <t>921</t>
+          <t>136</t>
         </is>
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>738405</t>
+          <t>68111</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>543357</t>
+          <t>53471</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>837687</t>
+          <t>82738</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -4343,112 +4347,112 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>8834</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4990</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>15053</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>21773</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>14545</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>29778</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>58</t>
         </is>
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>30607</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>22050</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>39720</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>3,02%</t>
         </is>
       </c>
     </row>
@@ -4456,112 +4460,112 @@
       <c r="A37" s="1" t="n"/>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>17</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10507</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6280</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>17684</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>59</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>24974</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16575</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>31937</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>76</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>35480</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>26456</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>45864</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -4569,225 +4573,229 @@
       <c r="A38" s="1" t="n"/>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>Otra persona del hogar</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>219</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>238937</t>
+          <t>813</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>207212</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>273970</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>20,02%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>4</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>208196</t>
+          <t>1559</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>107057</t>
+          <t>324</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>272263</t>
+          <t>4691</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>0,04%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
-          <t>532</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>447133</t>
+          <t>2372</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>319070</t>
+          <t>655</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>513431</t>
+          <t>5904</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>0,05%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>0,45%</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n"/>
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>57</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>113863</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>87267</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>138762</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>47,34%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>616204</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>588929</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>1526</t>
+          <t>636595</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>77,35%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>83,61%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1046</t>
         </is>
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>730067</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>691627</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1646</t>
+          <t>766542</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>72,87%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>76,51%</t>
         </is>
       </c>
     </row>
@@ -4795,112 +4803,112 @@
       <c r="A40" s="1" t="n"/>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>7042</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>35181</t>
+          <t>2325</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>57471</t>
+          <t>15714</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>122</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>75550</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>7328</t>
+          <t>62013</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>23496</t>
+          <t>91263</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>128</t>
         </is>
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>82592</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>42094</t>
+          <t>65979</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>76252</t>
+          <t>99808</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -4908,112 +4916,112 @@
       <c r="A41" s="1" t="n"/>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra persona del hogar</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>80</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>189514</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>15922</t>
+          <t>164563</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>35664</t>
+          <t>206611</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>85,91%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>254</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>242859</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>7729</t>
+          <t>219623</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>23076</t>
+          <t>275827</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>31,9%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>28,85%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>36,23%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>334</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>432374</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>26346</t>
+          <t>395350</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>51963</t>
+          <t>470003</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>46,91%</t>
         </is>
       </c>
     </row>
@@ -5021,112 +5029,112 @@
       <c r="A42" s="1" t="n"/>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>6</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>8953</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>19102</t>
+          <t>2476</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>41259</t>
+          <t>31495</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>120</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>61980</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>51060</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>18714</t>
+          <t>72986</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>126</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>70934</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>57911</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>53603</t>
+          <t>95593</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>9,54%</t>
         </is>
       </c>
     </row>
@@ -5134,229 +5142,225 @@
       <c r="A43" s="1" t="n"/>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>Otra situación</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>7973</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>1474</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>22845</t>
+          <t>21459</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>53</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>30600</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>1811</t>
+          <t>22603</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>13561</t>
+          <t>41812</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>57</t>
         </is>
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>38573</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>10984</t>
+          <t>28567</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>29758</t>
+          <t>54934</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>5,48%</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A44" s="1" t="n"/>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>Yo</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>294938</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>271475</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>318461</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>57,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>67,04%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr">
         <is>
-          <t>1199</t>
+          <t>62</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>796658</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>784781</t>
+          <t>24497</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>809097</t>
+          <t>40544</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>96,17%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
         <is>
-          <t>1539</t>
+          <t>62</t>
         </is>
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>1091596</t>
+          <t>31304</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>1060106</t>
+          <t>24165</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>1132236</t>
+          <t>40361</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5364,225 +5368,229 @@
       <c r="A45" s="1" t="n"/>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>213741</t>
+          <t>3871</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>191799</t>
+          <t>0</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>236293</t>
+          <t>20685</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
         <is>
-          <t>255</t>
+          <t>7</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>152338</t>
+          <t>5139</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>113166</t>
+          <t>2257</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>178440</t>
+          <t>11665</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>0,67%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13,45%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
         <is>
-          <t>502</t>
+          <t>8</t>
         </is>
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>366078</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>303432</t>
+          <t>3470</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>405244</t>
+          <t>23871</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n"/>
+      <c r="A46" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>Mi pareja y yo</t>
+          <t>Yo</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2171</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2063371</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1468582</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>2249215</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>61,13%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>66,63%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4825</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3272981</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>3229627</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>3328191</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>90,3%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>93,06%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6996</t>
         </is>
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>5336351</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>4676427</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>5565956</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>80,06%</t>
         </is>
       </c>
     </row>
@@ -5590,112 +5598,112 @@
       <c r="A47" s="1" t="n"/>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no es mi pareja y yo</t>
+          <t>Mi pareja</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1739</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1526795</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1123440</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>1670693</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>33,28%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>749774</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>631486</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>821798</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>22,98%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2918</t>
         </is>
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2276569</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1976122</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>2452334</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>32,75%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>35,27%</t>
         </is>
       </c>
     </row>
@@ -5708,107 +5716,107 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>139</t>
+          <t>728</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>139360</t>
+          <t>868289</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>119715</t>
+          <t>641915</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>165775</t>
+          <t>959267</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>25,72%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
         <is>
-          <t>234</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>143939</t>
+          <t>814532</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>106902</t>
+          <t>686353</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>169905</t>
+          <t>897324</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>373</t>
+          <t>1841</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>283299</t>
+          <t>1682821</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>226726</t>
+          <t>1458595</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>319019</t>
+          <t>1815130</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>26,11%</t>
         </is>
       </c>
     </row>
@@ -5816,112 +5824,112 @@
       <c r="A49" s="1" t="n"/>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>Una persona contratada para ello</t>
+          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>147</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104073</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79145</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1664</t>
+          <t>129742</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>293</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>142327</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>118621</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>163864</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>440</t>
         </is>
       </c>
       <c r="R49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>246399</t>
         </is>
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>213622</t>
         </is>
       </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
-          <t>1375</t>
+          <t>279212</t>
         </is>
       </c>
       <c r="U49" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>0,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
     </row>
@@ -5929,112 +5937,112 @@
       <c r="A50" s="1" t="n"/>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
+          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>120</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>90960</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>13966</t>
+          <t>68157</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>113220</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
         <is>
-          <t>107</t>
+          <t>216</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>48207</t>
+          <t>117079</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>34827</t>
+          <t>95786</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>58869</t>
+          <t>135861</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>7,0%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
         <is>
-          <t>136</t>
+          <t>336</t>
         </is>
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>68111</t>
+          <t>208039</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>54308</t>
+          <t>175519</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>81903</t>
+          <t>236315</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>3,4%</t>
         </is>
       </c>
     </row>
@@ -6042,112 +6050,112 @@
       <c r="A51" s="1" t="n"/>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
+          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>81</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>57508</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>4777</t>
+          <t>42282</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>15254</t>
+          <t>73563</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>172</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>81510</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>14243</t>
+          <t>65883</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>29397</t>
+          <t>98187</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>139018</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>116202</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>40172</t>
+          <t>162816</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,34%</t>
         </is>
       </c>
     </row>
@@ -6155,2498 +6163,117 @@
       <c r="A52" s="1" t="n"/>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
+          <t>Otra situación</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>31</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>276368</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>6020</t>
+          <t>30609</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>17514</t>
+          <t>1175751</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>20886</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>17970</t>
+          <t>13103</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>33627</t>
+          <t>30765</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>61</t>
         </is>
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>297254</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>26408</t>
+          <t>48991</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>44714</t>
+          <t>1105171</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>15,9%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n"/>
-      <c r="B53" s="3" t="inlineStr">
-        <is>
-          <t>Otra situación</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>813</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>5386</t>
-        </is>
-      </c>
-      <c r="G53" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K53" s="2" t="inlineStr">
-        <is>
-          <t>1559</t>
-        </is>
-      </c>
-      <c r="L53" s="2" t="inlineStr">
-        <is>
-          <t>327</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr">
-        <is>
-          <t>4593</t>
-        </is>
-      </c>
-      <c r="N53" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="O53" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="P53" s="2" t="inlineStr">
-        <is>
-          <t>0,55%</t>
-        </is>
-      </c>
-      <c r="Q53" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="R53" s="2" t="inlineStr">
-        <is>
-          <t>2372</t>
-        </is>
-      </c>
-      <c r="S53" s="2" t="inlineStr">
-        <is>
-          <t>690</t>
-        </is>
-      </c>
-      <c r="T53" s="2" t="inlineStr">
-        <is>
-          <t>6135</t>
-        </is>
-      </c>
-      <c r="U53" s="2" t="inlineStr">
-        <is>
-          <t>0,18%</t>
-        </is>
-      </c>
-      <c r="V53" s="2" t="inlineStr">
-        <is>
-          <t>0,05%</t>
-        </is>
-      </c>
-      <c r="W53" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="1" t="inlineStr">
-        <is>
-          <t>6.0</t>
-        </is>
-      </c>
-      <c r="B54" s="3" t="inlineStr">
-        <is>
-          <t>Yo</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
-        <is>
-          <t>113863</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="inlineStr">
-        <is>
-          <t>89370</t>
-        </is>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>142100</t>
-        </is>
-      </c>
-      <c r="G54" s="2" t="inlineStr">
-        <is>
-          <t>47,34%</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="inlineStr">
-        <is>
-          <t>37,16%</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="inlineStr">
-        <is>
-          <t>59,08%</t>
-        </is>
-      </c>
-      <c r="J54" s="2" t="inlineStr">
-        <is>
-          <t>989</t>
-        </is>
-      </c>
-      <c r="K54" s="2" t="inlineStr">
-        <is>
-          <t>616204</t>
-        </is>
-      </c>
-      <c r="L54" s="2" t="inlineStr">
-        <is>
-          <t>590994</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr">
-        <is>
-          <t>636590</t>
-        </is>
-      </c>
-      <c r="N54" s="2" t="inlineStr">
-        <is>
-          <t>80,93%</t>
-        </is>
-      </c>
-      <c r="O54" s="2" t="inlineStr">
-        <is>
-          <t>77,62%</t>
-        </is>
-      </c>
-      <c r="P54" s="2" t="inlineStr">
-        <is>
-          <t>83,61%</t>
-        </is>
-      </c>
-      <c r="Q54" s="2" t="inlineStr">
-        <is>
-          <t>1046</t>
-        </is>
-      </c>
-      <c r="R54" s="2" t="inlineStr">
-        <is>
-          <t>730067</t>
-        </is>
-      </c>
-      <c r="S54" s="2" t="inlineStr">
-        <is>
-          <t>687410</t>
-        </is>
-      </c>
-      <c r="T54" s="2" t="inlineStr">
-        <is>
-          <t>763855</t>
-        </is>
-      </c>
-      <c r="U54" s="2" t="inlineStr">
-        <is>
-          <t>72,87%</t>
-        </is>
-      </c>
-      <c r="V54" s="2" t="inlineStr">
-        <is>
-          <t>68,61%</t>
-        </is>
-      </c>
-      <c r="W54" s="2" t="inlineStr">
-        <is>
-          <t>76,24%</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="1" t="n"/>
-      <c r="B55" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>7042</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="inlineStr">
-        <is>
-          <t>2479</t>
-        </is>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>16475</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>2,93%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="J55" s="2" t="inlineStr">
-        <is>
-          <t>122</t>
-        </is>
-      </c>
-      <c r="K55" s="2" t="inlineStr">
-        <is>
-          <t>75550</t>
-        </is>
-      </c>
-      <c r="L55" s="2" t="inlineStr">
-        <is>
-          <t>62556</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr">
-        <is>
-          <t>90712</t>
-        </is>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
-        <is>
-          <t>9,92%</t>
-        </is>
-      </c>
-      <c r="O55" s="2" t="inlineStr">
-        <is>
-          <t>8,22%</t>
-        </is>
-      </c>
-      <c r="P55" s="2" t="inlineStr">
-        <is>
-          <t>11,91%</t>
-        </is>
-      </c>
-      <c r="Q55" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="R55" s="2" t="inlineStr">
-        <is>
-          <t>82592</t>
-        </is>
-      </c>
-      <c r="S55" s="2" t="inlineStr">
-        <is>
-          <t>66772</t>
-        </is>
-      </c>
-      <c r="T55" s="2" t="inlineStr">
-        <is>
-          <t>101308</t>
-        </is>
-      </c>
-      <c r="U55" s="2" t="inlineStr">
-        <is>
-          <t>8,24%</t>
-        </is>
-      </c>
-      <c r="V55" s="2" t="inlineStr">
-        <is>
-          <t>6,66%</t>
-        </is>
-      </c>
-      <c r="W55" s="2" t="inlineStr">
-        <is>
-          <t>10,11%</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="1" t="n"/>
-      <c r="B56" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F56" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="G56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P56" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="Q56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S56" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T56" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="U56" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V56" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W56" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="1" t="n"/>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no es mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P57" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="Q57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S57" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T57" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="U57" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V57" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W57" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="1" t="n"/>
-      <c r="B58" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona del hogar</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
-        <is>
-          <t>189514</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="inlineStr">
-        <is>
-          <t>163724</t>
-        </is>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>206697</t>
-        </is>
-      </c>
-      <c r="G58" s="2" t="inlineStr">
-        <is>
-          <t>78,8%</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>68,07%</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="inlineStr">
-        <is>
-          <t>85,94%</t>
-        </is>
-      </c>
-      <c r="J58" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
-      <c r="K58" s="2" t="inlineStr">
-        <is>
-          <t>242859</t>
-        </is>
-      </c>
-      <c r="L58" s="2" t="inlineStr">
-        <is>
-          <t>215813</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr">
-        <is>
-          <t>270884</t>
-        </is>
-      </c>
-      <c r="N58" s="2" t="inlineStr">
-        <is>
-          <t>31,9%</t>
-        </is>
-      </c>
-      <c r="O58" s="2" t="inlineStr">
-        <is>
-          <t>28,35%</t>
-        </is>
-      </c>
-      <c r="P58" s="2" t="inlineStr">
-        <is>
-          <t>35,58%</t>
-        </is>
-      </c>
-      <c r="Q58" s="2" t="inlineStr">
-        <is>
-          <t>334</t>
-        </is>
-      </c>
-      <c r="R58" s="2" t="inlineStr">
-        <is>
-          <t>432374</t>
-        </is>
-      </c>
-      <c r="S58" s="2" t="inlineStr">
-        <is>
-          <t>395970</t>
-        </is>
-      </c>
-      <c r="T58" s="2" t="inlineStr">
-        <is>
-          <t>472738</t>
-        </is>
-      </c>
-      <c r="U58" s="2" t="inlineStr">
-        <is>
-          <t>43,16%</t>
-        </is>
-      </c>
-      <c r="V58" s="2" t="inlineStr">
-        <is>
-          <t>39,52%</t>
-        </is>
-      </c>
-      <c r="W58" s="2" t="inlineStr">
-        <is>
-          <t>47,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="1" t="n"/>
-      <c r="B59" s="3" t="inlineStr">
-        <is>
-          <t>Una persona contratada para ello</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F59" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="G59" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I59" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr">
-        <is>
-          <t>1260</t>
-        </is>
-      </c>
-      <c r="N59" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
-      <c r="Q59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S59" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T59" s="2" t="inlineStr">
-        <is>
-          <t>1513</t>
-        </is>
-      </c>
-      <c r="U59" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V59" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W59" s="2" t="inlineStr">
-        <is>
-          <t>0,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="1" t="n"/>
-      <c r="B60" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
-        <is>
-          <t>8953</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="inlineStr">
-        <is>
-          <t>2364</t>
-        </is>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>32622</t>
-        </is>
-      </c>
-      <c r="G60" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="inlineStr">
-        <is>
-          <t>13,56%</t>
-        </is>
-      </c>
-      <c r="J60" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="K60" s="2" t="inlineStr">
-        <is>
-          <t>61980</t>
-        </is>
-      </c>
-      <c r="L60" s="2" t="inlineStr">
-        <is>
-          <t>50932</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr">
-        <is>
-          <t>72953</t>
-        </is>
-      </c>
-      <c r="N60" s="2" t="inlineStr">
-        <is>
-          <t>8,14%</t>
-        </is>
-      </c>
-      <c r="O60" s="2" t="inlineStr">
-        <is>
-          <t>6,69%</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="inlineStr">
-        <is>
-          <t>9,58%</t>
-        </is>
-      </c>
-      <c r="Q60" s="2" t="inlineStr">
-        <is>
-          <t>126</t>
-        </is>
-      </c>
-      <c r="R60" s="2" t="inlineStr">
-        <is>
-          <t>70934</t>
-        </is>
-      </c>
-      <c r="S60" s="2" t="inlineStr">
-        <is>
-          <t>58101</t>
-        </is>
-      </c>
-      <c r="T60" s="2" t="inlineStr">
-        <is>
-          <t>90198</t>
-        </is>
-      </c>
-      <c r="U60" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="V60" s="2" t="inlineStr">
-        <is>
-          <t>5,8%</t>
-        </is>
-      </c>
-      <c r="W60" s="2" t="inlineStr">
-        <is>
-          <t>9,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="1" t="n"/>
-      <c r="B61" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
-        <is>
-          <t>7973</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr">
-        <is>
-          <t>2076</t>
-        </is>
-      </c>
-      <c r="F61" s="2" t="inlineStr">
-        <is>
-          <t>28092</t>
-        </is>
-      </c>
-      <c r="G61" s="2" t="inlineStr">
-        <is>
-          <t>3,32%</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="I61" s="2" t="inlineStr">
-        <is>
-          <t>11,68%</t>
-        </is>
-      </c>
-      <c r="J61" s="2" t="inlineStr">
-        <is>
-          <t>53</t>
-        </is>
-      </c>
-      <c r="K61" s="2" t="inlineStr">
-        <is>
-          <t>30600</t>
-        </is>
-      </c>
-      <c r="L61" s="2" t="inlineStr">
-        <is>
-          <t>22448</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr">
-        <is>
-          <t>40472</t>
-        </is>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
-        <is>
-          <t>4,02%</t>
-        </is>
-      </c>
-      <c r="O61" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="P61" s="2" t="inlineStr">
-        <is>
-          <t>5,32%</t>
-        </is>
-      </c>
-      <c r="Q61" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
-      <c r="R61" s="2" t="inlineStr">
-        <is>
-          <t>38573</t>
-        </is>
-      </c>
-      <c r="S61" s="2" t="inlineStr">
-        <is>
-          <t>27257</t>
-        </is>
-      </c>
-      <c r="T61" s="2" t="inlineStr">
-        <is>
-          <t>54824</t>
-        </is>
-      </c>
-      <c r="U61" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="V61" s="2" t="inlineStr">
-        <is>
-          <t>2,72%</t>
-        </is>
-      </c>
-      <c r="W61" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="1" t="n"/>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>4080</t>
-        </is>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J62" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="K62" s="2" t="inlineStr">
-        <is>
-          <t>31304</t>
-        </is>
-      </c>
-      <c r="L62" s="2" t="inlineStr">
-        <is>
-          <t>23861</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr">
-        <is>
-          <t>40782</t>
-        </is>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
-        <is>
-          <t>4,11%</t>
-        </is>
-      </c>
-      <c r="O62" s="2" t="inlineStr">
-        <is>
-          <t>3,13%</t>
-        </is>
-      </c>
-      <c r="P62" s="2" t="inlineStr">
-        <is>
-          <t>5,36%</t>
-        </is>
-      </c>
-      <c r="Q62" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
-      <c r="R62" s="2" t="inlineStr">
-        <is>
-          <t>31304</t>
-        </is>
-      </c>
-      <c r="S62" s="2" t="inlineStr">
-        <is>
-          <t>24219</t>
-        </is>
-      </c>
-      <c r="T62" s="2" t="inlineStr">
-        <is>
-          <t>41994</t>
-        </is>
-      </c>
-      <c r="U62" s="2" t="inlineStr">
-        <is>
-          <t>3,12%</t>
-        </is>
-      </c>
-      <c r="V62" s="2" t="inlineStr">
-        <is>
-          <t>2,42%</t>
-        </is>
-      </c>
-      <c r="W62" s="2" t="inlineStr">
-        <is>
-          <t>4,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="1" t="n"/>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Otra situación</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>3871</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>20741</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
-        <is>
-          <t>1,61%</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="inlineStr">
-        <is>
-          <t>8,62%</t>
-        </is>
-      </c>
-      <c r="J63" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K63" s="2" t="inlineStr">
-        <is>
-          <t>5139</t>
-        </is>
-      </c>
-      <c r="L63" s="2" t="inlineStr">
-        <is>
-          <t>2194</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr">
-        <is>
-          <t>12383</t>
-        </is>
-      </c>
-      <c r="N63" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="O63" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="P63" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="Q63" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R63" s="2" t="inlineStr">
-        <is>
-          <t>9010</t>
-        </is>
-      </c>
-      <c r="S63" s="2" t="inlineStr">
-        <is>
-          <t>3355</t>
-        </is>
-      </c>
-      <c r="T63" s="2" t="inlineStr">
-        <is>
-          <t>24312</t>
-        </is>
-      </c>
-      <c r="U63" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="V63" s="2" t="inlineStr">
-        <is>
-          <t>0,33%</t>
-        </is>
-      </c>
-      <c r="W63" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="1" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Yo</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>2171</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>2063371</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>1579960</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>2239304</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr">
-        <is>
-          <t>61,13%</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>46,81%</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="inlineStr">
-        <is>
-          <t>66,34%</t>
-        </is>
-      </c>
-      <c r="J64" s="2" t="inlineStr">
-        <is>
-          <t>4825</t>
-        </is>
-      </c>
-      <c r="K64" s="2" t="inlineStr">
-        <is>
-          <t>3272981</t>
-        </is>
-      </c>
-      <c r="L64" s="2" t="inlineStr">
-        <is>
-          <t>3231401</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr">
-        <is>
-          <t>3335644</t>
-        </is>
-      </c>
-      <c r="N64" s="2" t="inlineStr">
-        <is>
-          <t>91,51%</t>
-        </is>
-      </c>
-      <c r="O64" s="2" t="inlineStr">
-        <is>
-          <t>90,35%</t>
-        </is>
-      </c>
-      <c r="P64" s="2" t="inlineStr">
-        <is>
-          <t>93,27%</t>
-        </is>
-      </c>
-      <c r="Q64" s="2" t="inlineStr">
-        <is>
-          <t>6996</t>
-        </is>
-      </c>
-      <c r="R64" s="2" t="inlineStr">
-        <is>
-          <t>5336351</t>
-        </is>
-      </c>
-      <c r="S64" s="2" t="inlineStr">
-        <is>
-          <t>4616227</t>
-        </is>
-      </c>
-      <c r="T64" s="2" t="inlineStr">
-        <is>
-          <t>5577279</t>
-        </is>
-      </c>
-      <c r="U64" s="2" t="inlineStr">
-        <is>
-          <t>76,76%</t>
-        </is>
-      </c>
-      <c r="V64" s="2" t="inlineStr">
-        <is>
-          <t>66,4%</t>
-        </is>
-      </c>
-      <c r="W64" s="2" t="inlineStr">
-        <is>
-          <t>80,22%</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="1" t="n"/>
-      <c r="B65" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>1739</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>1526795</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>1191427</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>1665912</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t>49,35%</t>
-        </is>
-      </c>
-      <c r="J65" s="2" t="inlineStr">
-        <is>
-          <t>1179</t>
-        </is>
-      </c>
-      <c r="K65" s="2" t="inlineStr">
-        <is>
-          <t>749774</t>
-        </is>
-      </c>
-      <c r="L65" s="2" t="inlineStr">
-        <is>
-          <t>608199</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr">
-        <is>
-          <t>819252</t>
-        </is>
-      </c>
-      <c r="N65" s="2" t="inlineStr">
-        <is>
-          <t>20,96%</t>
-        </is>
-      </c>
-      <c r="O65" s="2" t="inlineStr">
-        <is>
-          <t>17,01%</t>
-        </is>
-      </c>
-      <c r="P65" s="2" t="inlineStr">
-        <is>
-          <t>22,91%</t>
-        </is>
-      </c>
-      <c r="Q65" s="2" t="inlineStr">
-        <is>
-          <t>2918</t>
-        </is>
-      </c>
-      <c r="R65" s="2" t="inlineStr">
-        <is>
-          <t>2276569</t>
-        </is>
-      </c>
-      <c r="S65" s="2" t="inlineStr">
-        <is>
-          <t>1897716</t>
-        </is>
-      </c>
-      <c r="T65" s="2" t="inlineStr">
-        <is>
-          <t>2441300</t>
-        </is>
-      </c>
-      <c r="U65" s="2" t="inlineStr">
-        <is>
-          <t>32,75%</t>
-        </is>
-      </c>
-      <c r="V65" s="2" t="inlineStr">
-        <is>
-          <t>27,3%</t>
-        </is>
-      </c>
-      <c r="W65" s="2" t="inlineStr">
-        <is>
-          <t>35,12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="1" t="n"/>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>Mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="N66" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S66" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T66" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="U66" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V66" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W66" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="1" t="n"/>
-      <c r="B67" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no es mi pareja y yo</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I67" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="N67" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P67" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S67" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T67" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="U67" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V67" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W67" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="1" t="n"/>
-      <c r="B68" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona del hogar</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>728</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>868289</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>663513</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>966976</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr">
-        <is>
-          <t>25,72%</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>19,66%</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="inlineStr">
-        <is>
-          <t>28,65%</t>
-        </is>
-      </c>
-      <c r="J68" s="2" t="inlineStr">
-        <is>
-          <t>1113</t>
-        </is>
-      </c>
-      <c r="K68" s="2" t="inlineStr">
-        <is>
-          <t>814532</t>
-        </is>
-      </c>
-      <c r="L68" s="2" t="inlineStr">
-        <is>
-          <t>671015</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr">
-        <is>
-          <t>886779</t>
-        </is>
-      </c>
-      <c r="N68" s="2" t="inlineStr">
-        <is>
-          <t>22,77%</t>
-        </is>
-      </c>
-      <c r="O68" s="2" t="inlineStr">
-        <is>
-          <t>18,76%</t>
-        </is>
-      </c>
-      <c r="P68" s="2" t="inlineStr">
-        <is>
-          <t>24,79%</t>
-        </is>
-      </c>
-      <c r="Q68" s="2" t="inlineStr">
-        <is>
-          <t>1841</t>
-        </is>
-      </c>
-      <c r="R68" s="2" t="inlineStr">
-        <is>
-          <t>1682821</t>
-        </is>
-      </c>
-      <c r="S68" s="2" t="inlineStr">
-        <is>
-          <t>1418704</t>
-        </is>
-      </c>
-      <c r="T68" s="2" t="inlineStr">
-        <is>
-          <t>1817765</t>
-        </is>
-      </c>
-      <c r="U68" s="2" t="inlineStr">
-        <is>
-          <t>24,21%</t>
-        </is>
-      </c>
-      <c r="V68" s="2" t="inlineStr">
-        <is>
-          <t>20,41%</t>
-        </is>
-      </c>
-      <c r="W68" s="2" t="inlineStr">
-        <is>
-          <t>26,15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="1" t="n"/>
-      <c r="B69" s="3" t="inlineStr">
-        <is>
-          <t>Una persona contratada para ello</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>1965</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="H69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t>0,06%</t>
-        </is>
-      </c>
-      <c r="J69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="K69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr">
-        <is>
-          <t>1310</t>
-        </is>
-      </c>
-      <c r="N69" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P69" s="2" t="inlineStr">
-        <is>
-          <t>0,04%</t>
-        </is>
-      </c>
-      <c r="Q69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S69" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T69" s="2" t="inlineStr">
-        <is>
-          <t>1563</t>
-        </is>
-      </c>
-      <c r="U69" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="V69" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="W69" s="2" t="inlineStr">
-        <is>
-          <t>0,02%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="1" t="n"/>
-      <c r="B70" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y no esta contratada (familiares/vecinos/amigos)</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
-        <is>
-          <t>104073</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="inlineStr">
-        <is>
-          <t>80038</t>
-        </is>
-      </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>129749</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>3,08%</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="J70" s="2" t="inlineStr">
-        <is>
-          <t>293</t>
-        </is>
-      </c>
-      <c r="K70" s="2" t="inlineStr">
-        <is>
-          <t>142327</t>
-        </is>
-      </c>
-      <c r="L70" s="2" t="inlineStr">
-        <is>
-          <t>115189</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr">
-        <is>
-          <t>164650</t>
-        </is>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="O70" s="2" t="inlineStr">
-        <is>
-          <t>3,22%</t>
-        </is>
-      </c>
-      <c r="P70" s="2" t="inlineStr">
-        <is>
-          <t>4,6%</t>
-        </is>
-      </c>
-      <c r="Q70" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="R70" s="2" t="inlineStr">
-        <is>
-          <t>246399</t>
-        </is>
-      </c>
-      <c r="S70" s="2" t="inlineStr">
-        <is>
-          <t>207472</t>
-        </is>
-      </c>
-      <c r="T70" s="2" t="inlineStr">
-        <is>
-          <t>277744</t>
-        </is>
-      </c>
-      <c r="U70" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="V70" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="W70" s="2" t="inlineStr">
-        <is>
-          <t>4,0%</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="1" t="n"/>
-      <c r="B71" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que cobra de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
-        <is>
-          <t>90960</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="inlineStr">
-        <is>
-          <t>68728</t>
-        </is>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>113844</t>
-        </is>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t>2,69%</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>2,04%</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="J71" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K71" s="2" t="inlineStr">
-        <is>
-          <t>117079</t>
-        </is>
-      </c>
-      <c r="L71" s="2" t="inlineStr">
-        <is>
-          <t>95647</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr">
-        <is>
-          <t>137733</t>
-        </is>
-      </c>
-      <c r="N71" s="2" t="inlineStr">
-        <is>
-          <t>3,27%</t>
-        </is>
-      </c>
-      <c r="O71" s="2" t="inlineStr">
-        <is>
-          <t>2,67%</t>
-        </is>
-      </c>
-      <c r="P71" s="2" t="inlineStr">
-        <is>
-          <t>3,85%</t>
-        </is>
-      </c>
-      <c r="Q71" s="2" t="inlineStr">
-        <is>
-          <t>336</t>
-        </is>
-      </c>
-      <c r="R71" s="2" t="inlineStr">
-        <is>
-          <t>208039</t>
-        </is>
-      </c>
-      <c r="S71" s="2" t="inlineStr">
-        <is>
-          <t>175707</t>
-        </is>
-      </c>
-      <c r="T71" s="2" t="inlineStr">
-        <is>
-          <t>237608</t>
-        </is>
-      </c>
-      <c r="U71" s="2" t="inlineStr">
-        <is>
-          <t>2,99%</t>
-        </is>
-      </c>
-      <c r="V71" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="W71" s="2" t="inlineStr">
-        <is>
-          <t>3,42%</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="1" t="n"/>
-      <c r="B72" s="3" t="inlineStr">
-        <is>
-          <t>Otra persona que no reside en el hogar y que sí cobra aunque no de los ingresos del hogar</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
-        <is>
-          <t>57508</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="inlineStr">
-        <is>
-          <t>42349</t>
-        </is>
-      </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>75991</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>1,25%</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t>2,25%</t>
-        </is>
-      </c>
-      <c r="J72" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="K72" s="2" t="inlineStr">
-        <is>
-          <t>81510</t>
-        </is>
-      </c>
-      <c r="L72" s="2" t="inlineStr">
-        <is>
-          <t>64848</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr">
-        <is>
-          <t>96718</t>
-        </is>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="O72" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="P72" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="Q72" s="2" t="inlineStr">
-        <is>
-          <t>253</t>
-        </is>
-      </c>
-      <c r="R72" s="2" t="inlineStr">
-        <is>
-          <t>139018</t>
-        </is>
-      </c>
-      <c r="S72" s="2" t="inlineStr">
-        <is>
-          <t>115277</t>
-        </is>
-      </c>
-      <c r="T72" s="2" t="inlineStr">
-        <is>
-          <t>163946</t>
-        </is>
-      </c>
-      <c r="U72" s="2" t="inlineStr">
-        <is>
-          <t>2,0%</t>
-        </is>
-      </c>
-      <c r="V72" s="2" t="inlineStr">
-        <is>
-          <t>1,66%</t>
-        </is>
-      </c>
-      <c r="W72" s="2" t="inlineStr">
-        <is>
-          <t>2,36%</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="1" t="n"/>
-      <c r="B73" s="3" t="inlineStr">
-        <is>
-          <t>Otra situación</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>276368</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>30696</t>
-        </is>
-      </c>
-      <c r="F73" s="2" t="inlineStr">
-        <is>
-          <t>979893</t>
-        </is>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t>8,19%</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>0,91%</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t>29,03%</t>
-        </is>
-      </c>
-      <c r="J73" s="2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K73" s="2" t="inlineStr">
-        <is>
-          <t>20886</t>
-        </is>
-      </c>
-      <c r="L73" s="2" t="inlineStr">
-        <is>
-          <t>13189</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr">
-        <is>
-          <t>31775</t>
-        </is>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O73" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
-        </is>
-      </c>
-      <c r="P73" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="Q73" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="R73" s="2" t="inlineStr">
-        <is>
-          <t>297254</t>
-        </is>
-      </c>
-      <c r="S73" s="2" t="inlineStr">
-        <is>
-          <t>49552</t>
-        </is>
-      </c>
-      <c r="T73" s="2" t="inlineStr">
-        <is>
-          <t>1335688</t>
-        </is>
-      </c>
-      <c r="U73" s="2" t="inlineStr">
-        <is>
-          <t>4,28%</t>
-        </is>
-      </c>
-      <c r="V73" s="2" t="inlineStr">
-        <is>
-          <t>0,71%</t>
-        </is>
-      </c>
-      <c r="W73" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="A53" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (adultos)</t>
         </is>
@@ -8655,16 +6282,16 @@
   </sheetData>
   <mergeCells count="11">
     <mergeCell ref="J1:P1"/>
-    <mergeCell ref="A44:A53"/>
-    <mergeCell ref="A24:A33"/>
-    <mergeCell ref="A54:A63"/>
-    <mergeCell ref="A34:A43"/>
-    <mergeCell ref="A4:A13"/>
+    <mergeCell ref="A32:A38"/>
+    <mergeCell ref="A4:A10"/>
+    <mergeCell ref="A25:A31"/>
+    <mergeCell ref="A46:A52"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="A14:A23"/>
     <mergeCell ref="Q1:W1"/>
-    <mergeCell ref="A64:A73"/>
     <mergeCell ref="C1:I1"/>
+    <mergeCell ref="A18:A24"/>
+    <mergeCell ref="A11:A17"/>
+    <mergeCell ref="A39:A45"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/trans_orig/P3A$yo-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P3A$yo-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>361000</t>
+          <t>392403</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>338950</t>
+          <t>369266</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>380685</t>
+          <t>413799</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>67,09%</t>
+          <t>67,06%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>410776</t>
+          <t>449313</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>396025</t>
+          <t>435361</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>421260</t>
+          <t>460485</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>92,12%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,41%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>771776</t>
+          <t>841715</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>748144</t>
+          <t>811652</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>795793</t>
+          <t>866176</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>81,07%</t>
+          <t>81,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>78,59%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>299159</t>
+          <t>327450</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>273403</t>
+          <t>299737</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>321288</t>
+          <t>350385</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>59,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>54,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,59%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>155564</t>
+          <t>166828</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>138859</t>
+          <t>149877</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>172851</t>
+          <t>185151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>34,82%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>454723</t>
+          <t>494278</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>426355</t>
+          <t>460187</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484205</t>
+          <t>523385</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>47,77%</t>
+          <t>47,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>44,79%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>50,86%</t>
+          <t>50,41%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>97633</t>
+          <t>103157</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>80472</t>
+          <t>85711</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>120302</t>
+          <t>125799</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,33%</t>
+          <t>18,73%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>15,93%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>100822</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>87018</t>
+          <t>92903</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>117620</t>
+          <t>126614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>22,57%</t>
+          <t>22,05%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19,48%</t>
+          <t>19,05%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>198455</t>
+          <t>210704</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>173927</t>
+          <t>187236</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>225831</t>
+          <t>240769</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,19%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4124</t>
+          <t>4435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13337</t>
+          <t>15221</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>4082</t>
+          <t>4833</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1845</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>9319</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,22 +1134,22 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11653</t>
+          <t>12966</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7384</t>
+          <t>8051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>17822</t>
+          <t>19985</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,92%</t>
         </is>
       </c>
     </row>
@@ -1177,32 +1177,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>29293</t>
+          <t>31763</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>20588</t>
+          <t>23485</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>40618</t>
+          <t>44847</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1212,32 +1212,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>31060</t>
+          <t>34231</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>23396</t>
+          <t>25901</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>40447</t>
+          <t>44533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>60353</t>
+          <t>65994</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>48220</t>
+          <t>54857</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>74275</t>
+          <t>82402</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,94%</t>
         </is>
       </c>
     </row>
@@ -1290,32 +1290,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>7157</t>
+          <t>7336</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3594</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12285</t>
+          <t>14719</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1191</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1335,12 +1335,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>3995</t>
+          <t>4213</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1350,7 +1350,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>8618</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>4504</t>
+          <t>4371</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>14072</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1403,32 +1403,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>6186</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1622</t>
+          <t>2485</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11958</t>
+          <t>13248</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1438,32 +1438,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>6817</t>
+          <t>9243</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>4249</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>14295</t>
+          <t>18218</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1473,32 +1473,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>11895</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>6278</t>
+          <t>8429</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>20626</t>
+          <t>26058</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,51%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>313528</t>
+          <t>335066</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>291292</t>
+          <t>313046</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>333847</t>
+          <t>356674</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,9%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>359996</t>
+          <t>398221</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>348532</t>
+          <t>386415</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>367853</t>
+          <t>406390</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>94,1%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>673524</t>
+          <t>733287</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>647732</t>
+          <t>706385</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>696309</t>
+          <t>756698</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>80,73%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>77,64%</t>
+          <t>77,98%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>83,53%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>236580</t>
+          <t>255472</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>215924</t>
+          <t>232385</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>257682</t>
+          <t>277038</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>52,37%</t>
+          <t>52,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,8%</t>
+          <t>48,14%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>113162</t>
+          <t>120515</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>99474</t>
+          <t>103598</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>129229</t>
+          <t>137272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>349742</t>
+          <t>375987</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>322873</t>
+          <t>346623</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>377666</t>
+          <t>404680</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>38,7%</t>
+          <t>38,26%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>44,67%</t>
         </is>
       </c>
     </row>
@@ -1746,32 +1746,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>114817</t>
+          <t>122001</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>95259</t>
+          <t>102246</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>137476</t>
+          <t>145330</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>25,27%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,43%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1781,32 +1781,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>82999</t>
+          <t>88631</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>74431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98233</t>
+          <t>104860</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,69%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>197816</t>
+          <t>210632</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>175409</t>
+          <t>185295</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>227521</t>
+          <t>239107</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>26,4%</t>
         </is>
       </c>
     </row>
@@ -1859,32 +1859,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8699</t>
+          <t>9002</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4775</t>
+          <t>4694</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15505</t>
+          <t>16087</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1894,32 +1894,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>5755</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3135</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>10612</t>
+          <t>13627</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>14453</t>
+          <t>16573</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>9238</t>
+          <t>10760</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>21559</t>
+          <t>25465</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1972,32 +1972,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14767</t>
+          <t>16080</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9219</t>
+          <t>9705</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>24360</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2007,32 +2007,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12447</t>
+          <t>15734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>8182</t>
+          <t>10477</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>18215</t>
+          <t>22936</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>3,25%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>27214</t>
+          <t>31814</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>19118</t>
+          <t>23134</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>36334</t>
+          <t>40809</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -2085,32 +2085,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3285</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>966</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8215</t>
+          <t>8654</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2120,32 +2120,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>5058</t>
+          <t>5780</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2344</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>9851</t>
+          <t>9919</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,17 +2155,17 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>8342</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4841</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>15130</t>
+          <t>15793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -2198,32 +2198,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9153</t>
+          <t>9377</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4268</t>
+          <t>4482</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17219</t>
+          <t>17317</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,94%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2233,32 +2233,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1782</t>
+          <t>1818</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>409</t>
+          <t>436</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>5012</t>
+          <t>5605</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>0,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2268,32 +2268,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>10936</t>
+          <t>11196</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>5682</t>
+          <t>5763</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>18789</t>
+          <t>20326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -2315,32 +2315,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>281530</t>
+          <t>306191</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109684</t>
+          <t>285141</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>453787</t>
+          <t>327254</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>67,91%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2350,32 +2350,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>151682</t>
+          <t>170259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>141368</t>
+          <t>158993</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>157380</t>
+          <t>176688</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,98%</t>
+          <t>85,06%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>433212</t>
+          <t>476449</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>202352</t>
+          <t>450598</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>620429</t>
+          <t>498268</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>68,42%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>75,66%</t>
         </is>
       </c>
     </row>
@@ -2428,32 +2428,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>241950</t>
+          <t>271032</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>97754</t>
+          <t>249655</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>394221</t>
+          <t>294528</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>36,21%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>52,94%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2463,32 +2463,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43079</t>
+          <t>47697</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34708</t>
+          <t>39326</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>52984</t>
+          <t>59592</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,9%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>21,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,85%</t>
+          <t>31,88%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>285029</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>129610</t>
+          <t>294290</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>408863</t>
+          <t>345018</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>48,4%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>52,39%</t>
         </is>
       </c>
     </row>
@@ -2541,32 +2541,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>88029</t>
+          <t>100342</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>82251</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>147620</t>
+          <t>118571</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2576,32 +2576,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>35717</t>
+          <t>40447</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27068</t>
+          <t>31366</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>46115</t>
+          <t>52630</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>123745</t>
+          <t>140789</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>58610</t>
+          <t>120063</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>181840</t>
+          <t>163620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>18,23%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>21,79%</t>
+          <t>24,85%</t>
         </is>
       </c>
     </row>
@@ -2654,32 +2654,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>13877</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>4197</t>
+          <t>8480</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>26438</t>
+          <t>21378</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2689,32 +2689,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>6530</t>
+          <t>7009</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3985</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11013</t>
+          <t>12000</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,42%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>20406</t>
+          <t>21130</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8012</t>
+          <t>14833</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>32286</t>
+          <t>31001</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>3,21%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -2767,32 +2767,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>6349</t>
+          <t>9011</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1684</t>
+          <t>4424</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>12994</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2802,32 +2802,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>6251</t>
+          <t>7386</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3335</t>
+          <t>3964</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,7%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>12600</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4368</t>
+          <t>10405</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>21322</t>
+          <t>25563</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -2880,32 +2880,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10254</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>2777</t>
+          <t>5810</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>16499</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,42%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2915,32 +2915,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>6643</t>
+          <t>7753</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3586</t>
+          <t>4235</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>11390</t>
+          <t>13846</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>16227</t>
+          <t>18007</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>5956</t>
+          <t>12180</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26209</t>
+          <t>26845</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3003,12 +3003,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>498119</t>
+          <t>5740</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3063,7 +3063,7 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>244680</t>
+          <t>1141</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>558002</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>29,32%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>698511</t>
+          <t>755615</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>664665</t>
+          <t>719293</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>731240</t>
+          <t>788114</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>67,5%</t>
+          <t>66,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>70,66%</t>
+          <t>69,63%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>937664</t>
+          <t>816354</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>920824</t>
+          <t>803762</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>957085</t>
+          <t>828443</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>95,87%</t>
+          <t>94,79%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1636174</t>
+          <t>1571969</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1579451</t>
+          <t>1528568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1757817</t>
+          <t>1609330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>78,47%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>87,33%</t>
+          <t>80,75%</t>
         </is>
       </c>
     </row>
@@ -3223,32 +3223,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>528324</t>
+          <t>587623</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>490777</t>
+          <t>555509</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>563866</t>
+          <t>624355</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,92%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>47,43%</t>
+          <t>49,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>54,49%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3258,32 +3258,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>210081</t>
+          <t>230379</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>115126</t>
+          <t>206784</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>275424</t>
+          <t>253266</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>29,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>738405</t>
+          <t>818001</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>506191</t>
+          <t>773834</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>833683</t>
+          <t>860512</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>25,15%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>41,42%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -3336,32 +3336,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>238937</t>
+          <t>262851</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>207804</t>
+          <t>228626</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>276076</t>
+          <t>296305</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>20,08%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>26,68%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3371,32 +3371,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>208196</t>
+          <t>230091</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>123209</t>
+          <t>207331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>274137</t>
+          <t>254227</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>29,52%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>447133</t>
+          <t>492942</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>311024</t>
+          <t>454211</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>518608</t>
+          <t>537370</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,96%</t>
         </is>
       </c>
     </row>
@@ -3449,32 +3449,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>45069</t>
+          <t>47692</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34763</t>
+          <t>36753</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>56955</t>
+          <t>60516</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3484,32 +3484,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>15773</t>
+          <t>17822</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>8503</t>
+          <t>12489</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>23983</t>
+          <t>24755</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>60841</t>
+          <t>65514</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>43506</t>
+          <t>54104</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>75403</t>
+          <t>81470</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3562,17 +3562,17 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>23744</t>
+          <t>25884</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>15535</t>
+          <t>17889</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>35293</t>
+          <t>40043</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3597,32 +3597,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>14947</t>
+          <t>16022</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>7597</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>22472</t>
+          <t>22718</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>41907</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>25432</t>
+          <t>32029</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>52090</t>
+          <t>55508</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>26977</t>
+          <t>29277</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>20143</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>40347</t>
+          <t>44402</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>12340</t>
+          <t>13716</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>5703</t>
+          <t>9378</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>18832</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>39317</t>
+          <t>42993</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>26219</t>
+          <t>33719</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>53978</t>
+          <t>57645</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,89%</t>
         </is>
       </c>
     </row>
@@ -3788,32 +3788,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>12773</t>
+          <t>15166</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>6504</t>
+          <t>8708</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>22474</t>
+          <t>26284</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3823,32 +3823,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>5588</t>
+          <t>6278</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1748</t>
+          <t>2404</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12108</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3858,32 +3858,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>18362</t>
+          <t>21444</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>10429</t>
+          <t>12959</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>30110</t>
+          <t>33029</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3905,32 +3905,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>294938</t>
+          <t>355993</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>269891</t>
+          <t>331387</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>315728</t>
+          <t>380813</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>56,81%</t>
+          <t>58,35%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>67,05%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3940,32 +3940,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>796658</t>
+          <t>782244</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>783655</t>
+          <t>771195</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>807936</t>
+          <t>791497</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,82%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>96,03%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>1091596</t>
+          <t>1138237</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1061203</t>
+          <t>1108476</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>1138782</t>
+          <t>1166959</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>82,92%</t>
+          <t>81,37%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>80,62%</t>
+          <t>79,24%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>83,42%</t>
         </is>
       </c>
     </row>
@@ -4018,32 +4018,32 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>213741</t>
+          <t>254400</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>190366</t>
+          <t>230392</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>236558</t>
+          <t>280426</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>44,99%</t>
+          <t>44,79%</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>40,07%</t>
+          <t>40,56%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4053,32 +4053,32 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>152338</t>
+          <t>164940</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>115670</t>
+          <t>147780</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>180429</t>
+          <t>186615</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>19,85%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>366078</t>
+          <t>419340</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>292821</t>
+          <t>386066</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>405993</t>
+          <t>451832</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>30,84%</t>
+          <t>32,3%</t>
         </is>
       </c>
     </row>
@@ -4131,32 +4131,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>139360</t>
+          <t>157031</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>117800</t>
+          <t>134767</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>163903</t>
+          <t>181140</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>29,34%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>23,73%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4166,32 +4166,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>143939</t>
+          <t>165793</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>108190</t>
+          <t>145674</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>168805</t>
+          <t>185752</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12,86%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>283299</t>
+          <t>322825</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>229222</t>
+          <t>290328</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>317858</t>
+          <t>354843</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>20,76%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>25,37%</t>
         </is>
       </c>
     </row>
@@ -4244,32 +4244,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>19904</t>
+          <t>20732</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>13220</t>
+          <t>14310</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>28933</t>
+          <t>30687</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4279,32 +4279,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>48207</t>
+          <t>50972</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>33957</t>
+          <t>41548</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>59573</t>
+          <t>60752</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,31%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>68111</t>
+          <t>71704</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>53471</t>
+          <t>59506</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>82738</t>
+          <t>87056</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,22%</t>
         </is>
       </c>
     </row>
@@ -4357,32 +4357,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>8834</t>
+          <t>9156</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>4990</t>
+          <t>5031</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>15053</t>
+          <t>15456</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4392,32 +4392,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>24035</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>14545</t>
+          <t>17808</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>29778</t>
+          <t>32782</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>2,14%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>30607</t>
+          <t>33191</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>22050</t>
+          <t>25537</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>39720</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,13%</t>
         </is>
       </c>
     </row>
@@ -4470,32 +4470,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>10507</t>
+          <t>11697</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>6280</t>
+          <t>6388</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>17684</t>
+          <t>18629</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4505,32 +4505,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>24974</t>
+          <t>25724</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>16575</t>
+          <t>19987</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>31937</t>
+          <t>33891</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>35480</t>
+          <t>37421</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>29048</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>45864</t>
+          <t>47289</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>813</t>
+          <t>889</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
@@ -4593,12 +4593,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4432</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4608,7 +4608,7 @@
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr">
@@ -4618,32 +4618,32 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>1559</t>
+          <t>2508</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>752</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>5968</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>0,04%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="Q38" s="2" t="inlineStr">
@@ -4653,39 +4653,39 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>2372</t>
+          <t>3397</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>655</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>5904</t>
+          <t>8065</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="V38" s="2" t="inlineStr">
         <is>
-          <t>0,05%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -4700,32 +4700,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>113863</t>
+          <t>105643</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>87267</t>
+          <t>83232</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>138762</t>
+          <t>128102</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>47,34%</t>
+          <t>44,53%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>57,7%</t>
+          <t>54,0%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4735,32 +4735,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>616204</t>
+          <t>683574</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>588929</t>
+          <t>656695</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>636595</t>
+          <t>709123</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>80,93%</t>
+          <t>80,97%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,78%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>83,61%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4770,32 +4770,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>730067</t>
+          <t>789217</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>691627</t>
+          <t>746972</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>766542</t>
+          <t>826605</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>72,87%</t>
+          <t>72,97%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>76,51%</t>
+          <t>76,43%</t>
         </is>
       </c>
     </row>
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>7042</t>
+          <t>7724</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>2325</t>
+          <t>2996</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>15714</t>
+          <t>17561</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4848,32 +4848,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>75550</t>
+          <t>81922</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>62013</t>
+          <t>66775</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>91263</t>
+          <t>98547</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>9,92%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4883,27 +4883,27 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>82592</t>
+          <t>89646</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>65979</t>
+          <t>75208</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>99808</t>
+          <t>107732</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
@@ -4926,32 +4926,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>189514</t>
+          <t>186853</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>164563</t>
+          <t>165855</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>206611</t>
+          <t>203501</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>68,42%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>85,91%</t>
+          <t>85,78%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4961,32 +4961,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>242859</t>
+          <t>270901</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>219623</t>
+          <t>239933</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>275827</t>
+          <t>300933</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>28,85%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>36,23%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -4996,32 +4996,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>432374</t>
+          <t>457754</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>395350</t>
+          <t>418398</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>470003</t>
+          <t>499234</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>43,16%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>39,46%</t>
+          <t>38,69%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,16%</t>
         </is>
       </c>
     </row>
@@ -5039,32 +5039,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>8953</t>
+          <t>5939</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>2476</t>
+          <t>2081</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>31495</t>
+          <t>16944</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5074,32 +5074,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>61980</t>
+          <t>65837</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>51060</t>
+          <t>54088</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>72986</t>
+          <t>79196</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5109,32 +5109,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>70934</t>
+          <t>71776</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>57911</t>
+          <t>60217</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>95593</t>
+          <t>87242</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>8,07%</t>
         </is>
       </c>
     </row>
@@ -5152,32 +5152,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>7973</t>
+          <t>7665</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>1474</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>21459</t>
+          <t>22115</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>0,61%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr">
@@ -5187,32 +5187,32 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>30600</t>
+          <t>33076</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>22603</t>
+          <t>24353</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>43650</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="Q43" s="2" t="inlineStr">
@@ -5222,32 +5222,32 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>38573</t>
+          <t>40742</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>28567</t>
+          <t>29678</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>54934</t>
+          <t>56723</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -5300,32 +5300,32 @@
       </c>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>24497</t>
+          <t>25472</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>40544</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,93%</t>
         </is>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="Q44" s="2" t="inlineStr">
@@ -5335,32 +5335,32 @@
       </c>
       <c r="R44" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>33185</t>
         </is>
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>24165</t>
+          <t>25274</t>
         </is>
       </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
-          <t>40361</t>
+          <t>43421</t>
         </is>
       </c>
       <c r="U44" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,01%</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>3871</t>
+          <t>3415</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
@@ -5388,12 +5388,12 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>20685</t>
+          <t>16731</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr">
@@ -5413,32 +5413,32 @@
       </c>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>5139</t>
+          <t>5719</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2257</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>11665</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="Q45" s="2" t="inlineStr">
@@ -5448,32 +5448,32 @@
       </c>
       <c r="R45" s="2" t="inlineStr">
         <is>
-          <t>9010</t>
+          <t>9134</t>
         </is>
       </c>
       <c r="S45" s="2" t="inlineStr">
         <is>
-          <t>3470</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
-          <t>23871</t>
+          <t>23475</t>
         </is>
       </c>
       <c r="U45" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,17%</t>
         </is>
       </c>
     </row>
@@ -5495,32 +5495,32 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>2063371</t>
+          <t>2250911</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>1468582</t>
+          <t>2191844</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>2249215</t>
+          <t>2315368</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>61,13%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>66,63%</t>
+          <t>67,27%</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr">
@@ -5530,32 +5530,32 @@
       </c>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>3272981</t>
+          <t>3299966</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>3229627</t>
+          <t>3259600</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>3328191</t>
+          <t>3334112</t>
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>91,51%</t>
+          <t>90,8%</t>
         </is>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>90,3%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
-          <t>93,06%</t>
+          <t>91,74%</t>
         </is>
       </c>
       <c r="Q46" s="2" t="inlineStr">
@@ -5565,32 +5565,32 @@
       </c>
       <c r="R46" s="2" t="inlineStr">
         <is>
-          <t>5336351</t>
+          <t>5550875</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>4676427</t>
+          <t>5463609</t>
         </is>
       </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
-          <t>5565956</t>
+          <t>5624402</t>
         </is>
       </c>
       <c r="U46" s="2" t="inlineStr">
         <is>
-          <t>76,76%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>67,27%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>80,06%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -5608,32 +5608,32 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>1526795</t>
+          <t>1703701</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>1123440</t>
+          <t>1637696</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1670693</t>
+          <t>1766642</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>49,5%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>33,28%</t>
+          <t>47,58%</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr">
@@ -5643,32 +5643,32 @@
       </c>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>749774</t>
+          <t>812281</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>631486</t>
+          <t>766426</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>821798</t>
+          <t>853049</t>
         </is>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
-          <t>22,98%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="Q47" s="2" t="inlineStr">
@@ -5678,32 +5678,32 @@
       </c>
       <c r="R47" s="2" t="inlineStr">
         <is>
-          <t>2276569</t>
+          <t>2515981</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>1976122</t>
+          <t>2439039</t>
         </is>
       </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
-          <t>2452334</t>
+          <t>2600231</t>
         </is>
       </c>
       <c r="U47" s="2" t="inlineStr">
         <is>
-          <t>32,75%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>35,27%</t>
+          <t>36,75%</t>
         </is>
       </c>
     </row>
@@ -5721,32 +5721,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>868289</t>
+          <t>932236</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>641915</t>
+          <t>870752</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>959267</t>
+          <t>996962</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>25,72%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr">
@@ -5756,32 +5756,32 @@
       </c>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>814532</t>
+          <t>903410</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>686353</t>
+          <t>856049</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>897324</t>
+          <t>958432</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>23,56%</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
-          <t>25,09%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="Q48" s="2" t="inlineStr">
@@ -5791,32 +5791,32 @@
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>1682821</t>
+          <t>1835645</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>1458595</t>
+          <t>1755575</t>
         </is>
       </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
-          <t>1815130</t>
+          <t>1921141</t>
         </is>
       </c>
       <c r="U48" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>27,15%</t>
         </is>
       </c>
     </row>
@@ -5834,32 +5834,32 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>104073</t>
+          <t>105619</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>79145</t>
+          <t>88466</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>129742</t>
+          <t>124379</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr">
@@ -5869,67 +5869,67 @@
       </c>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>142327</t>
+          <t>154044</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>118621</t>
+          <t>136299</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>163864</t>
+          <t>171876</t>
         </is>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>4,73%</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr">
+        <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="R49" s="2" t="inlineStr">
+        <is>
+          <t>259663</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>234723</t>
+        </is>
+      </c>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>285484</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>3,67%</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
           <t>3,32%</t>
         </is>
       </c>
-      <c r="P49" s="2" t="inlineStr">
-        <is>
-          <t>4,58%</t>
-        </is>
-      </c>
-      <c r="Q49" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
-      <c r="R49" s="2" t="inlineStr">
-        <is>
-          <t>246399</t>
-        </is>
-      </c>
-      <c r="S49" s="2" t="inlineStr">
-        <is>
-          <t>213622</t>
-        </is>
-      </c>
-      <c r="T49" s="2" t="inlineStr">
-        <is>
-          <t>279212</t>
-        </is>
-      </c>
-      <c r="U49" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="V49" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,03%</t>
         </is>
       </c>
     </row>
@@ -5947,32 +5947,32 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>90960</t>
+          <t>99560</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>68157</t>
+          <t>81457</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>113220</t>
+          <t>122377</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr">
@@ -5982,32 +5982,32 @@
       </c>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>117079</t>
+          <t>130485</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>95786</t>
+          <t>113841</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>135861</t>
+          <t>149700</t>
         </is>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q50" s="2" t="inlineStr">
@@ -6017,32 +6017,32 @@
       </c>
       <c r="R50" s="2" t="inlineStr">
         <is>
-          <t>208039</t>
+          <t>230045</t>
         </is>
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>175519</t>
+          <t>205681</t>
         </is>
       </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
-          <t>236315</t>
+          <t>258906</t>
         </is>
       </c>
       <c r="U50" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,66%</t>
         </is>
       </c>
     </row>
@@ -6060,32 +6060,32 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>57508</t>
+          <t>61849</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>42282</t>
+          <t>47741</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>73563</t>
+          <t>77038</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>2,18%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr">
@@ -6095,32 +6095,32 @@
       </c>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>81510</t>
+          <t>87440</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>65883</t>
+          <t>74412</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>98187</t>
+          <t>101556</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q51" s="2" t="inlineStr">
@@ -6130,32 +6130,32 @@
       </c>
       <c r="R51" s="2" t="inlineStr">
         <is>
-          <t>139018</t>
+          <t>149289</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>116202</t>
+          <t>130865</t>
         </is>
       </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
-          <t>162816</t>
+          <t>170970</t>
         </is>
       </c>
       <c r="U51" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,42%</t>
         </is>
       </c>
     </row>
@@ -6173,32 +6173,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>276368</t>
+          <t>36174</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>30609</t>
+          <t>24420</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1175751</t>
+          <t>52983</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr">
@@ -6208,32 +6208,32 @@
       </c>
       <c r="K52" s="2" t="inlineStr">
         <is>
-          <t>20886</t>
+          <t>25567</t>
         </is>
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>13103</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>30765</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="Q52" s="2" t="inlineStr">
@@ -6243,32 +6243,32 @@
       </c>
       <c r="R52" s="2" t="inlineStr">
         <is>
-          <t>297254</t>
+          <t>61741</t>
         </is>
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>48991</t>
+          <t>45661</t>
         </is>
       </c>
       <c r="T52" s="2" t="inlineStr">
         <is>
-          <t>1105171</t>
+          <t>83099</t>
         </is>
       </c>
       <c r="U52" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>1,17%</t>
         </is>
       </c>
     </row>
